--- a/data/trans_orig/P33B_R1-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P33B_R1-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>128582</t>
+          <t>137830</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>112801</t>
+          <t>120674</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>147569</t>
+          <t>158464</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,67 +760,67 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>277481</t>
+          <t>309217</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>255486</t>
+          <t>288043</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>297990</t>
+          <t>328623</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>35,07%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>40,01%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>447047</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>418565</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>474777</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>31,94%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>29,9%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>33,92%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>39,56%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>715</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>406062</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>377577</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>430482</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>32,02%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>29,77%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>33,95%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>386356</t>
+          <t>440699</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>367369</t>
+          <t>420065</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>402137</t>
+          <t>457855</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,67 +873,67 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>475687</t>
+          <t>512098</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>455178</t>
+          <t>492692</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>497682</t>
+          <t>533272</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>64,93%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>952798</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>925068</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>981280</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>68,06%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>66,08%</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1402</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>862045</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>837625</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>890530</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>67,98%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>66,05%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,1%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1268107</t>
+          <t>1399845</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1268107</t>
+          <t>1399845</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1268107</t>
+          <t>1399845</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>222433</t>
+          <t>238586</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>158584</t>
+          <t>212093</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>263806</t>
+          <t>272385</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>337750</t>
+          <t>382777</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>240086</t>
+          <t>355255</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>388033</t>
+          <t>415756</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>560183</t>
+          <t>621364</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>449083</t>
+          <t>578587</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>628391</t>
+          <t>668592</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2066864</t>
+          <t>1990899</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2025491</t>
+          <t>1957100</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2130713</t>
+          <t>2017392</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1899508</t>
+          <t>1788047</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1849225</t>
+          <t>1755068</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1997172</t>
+          <t>1815569</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3966372</t>
+          <t>3778944</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3898164</t>
+          <t>3731716</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4077472</t>
+          <t>3821721</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>86,85%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2289297</t>
+          <t>2229485</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2289297</t>
+          <t>2229485</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2289297</t>
+          <t>2229485</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237258</t>
+          <t>2170824</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237258</t>
+          <t>2170824</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237258</t>
+          <t>2170824</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4526555</t>
+          <t>4400308</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4526555</t>
+          <t>4400308</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4526555</t>
+          <t>4400308</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>65229</t>
+          <t>72931</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50868</t>
+          <t>57133</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82569</t>
+          <t>90745</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>90239</t>
+          <t>101330</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>76851</t>
+          <t>86159</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106916</t>
+          <t>118351</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>155468</t>
+          <t>174261</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>135246</t>
+          <t>151765</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>179317</t>
+          <t>198050</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>581394</t>
+          <t>638656</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>564054</t>
+          <t>620842</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>595755</t>
+          <t>654454</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>570224</t>
+          <t>633547</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>553547</t>
+          <t>616526</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>583612</t>
+          <t>648718</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1151618</t>
+          <t>1272203</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1127769</t>
+          <t>1248414</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1171840</t>
+          <t>1294699</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,51%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>416243</t>
+          <t>449347</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>324201</t>
+          <t>413057</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>467710</t>
+          <t>491810</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>705470</t>
+          <t>793324</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>578078</t>
+          <t>752797</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>772427</t>
+          <t>838646</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1121713</t>
+          <t>1242671</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>977673</t>
+          <t>1188012</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1213800</t>
+          <t>1303181</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3034616</t>
+          <t>3070254</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2983149</t>
+          <t>3027791</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3126658</t>
+          <t>3106544</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2945419</t>
+          <t>2933692</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2878462</t>
+          <t>2888370</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3072811</t>
+          <t>2974219</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5980035</t>
+          <t>6003946</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5887948</t>
+          <t>5943436</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6124075</t>
+          <t>6058605</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>83,61%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3450859</t>
+          <t>3519601</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3450859</t>
+          <t>3519601</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3450859</t>
+          <t>3519601</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3650889</t>
+          <t>3727016</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3650889</t>
+          <t>3727016</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3650889</t>
+          <t>3727016</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7101748</t>
+          <t>7246617</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7101748</t>
+          <t>7246617</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7101748</t>
+          <t>7246617</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
